--- a/public/documents/pieces-reponse-1/R1-biere-freinte.xlsx
+++ b/public/documents/pieces-reponse-1/R1-biere-freinte.xlsx
@@ -8,10 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="1. Futs achetes et biere servie" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2. Du fut achete au facturable" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. La freinte retenue" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3. Les deux taux du service" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="4. Le 15 % de fin de methode" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. Litres et euros" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. Les deux abattements" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. Calendrier de la biere" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. Futs perimes a 30 jours" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8. Les niveaux en presence" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -823,18 +826,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,42 +860,32 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Nombre de fûts de 8 L achetés</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>Fûts achetés (L)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Nombre de fûts de 8 L</t>
-        </is>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Volume résiduel non tirable 1,5 % (L) - manuel Heineken Blade</t>
+          <t>Bière réellement sortie du fût, lue en caisse (L)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Freinte au taux retenu 10 % (L)</t>
+          <t>Taux retenu</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Volume facturable à 10 % (L)</t>
+          <t>Freinte retenue (L) = 10 % de la bière sortie du fût</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Freinte à la borne haute 20 % (L)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Volume facturable à 20 % (L)</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Bière servie en caisse (L)</t>
+          <t>dont résidu de fin de fût, au seuil du constructeur (L)</t>
         </is>
       </c>
     </row>
@@ -905,28 +896,24 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>792</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>99</v>
-      </c>
       <c r="D5" s="5" t="n">
+        <v>431.7</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>11.88</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>712.8</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>633.6</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>431.7</v>
       </c>
     </row>
     <row r="6">
@@ -936,28 +923,24 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>632</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>79</v>
-      </c>
       <c r="D6" s="5" t="n">
+        <v>391.1</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>9.48</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>568.8</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>126.4</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>505.6</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>391.1</v>
       </c>
     </row>
     <row r="7">
@@ -967,28 +950,24 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>672</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>84</v>
-      </c>
       <c r="D7" s="5" t="n">
+        <v>396.4</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="G7" s="5" t="n">
         <v>10.08</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>604.8</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>134.4</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>537.6</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>396.4</v>
       </c>
     </row>
     <row r="8">
@@ -998,28 +977,24 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
+        <v>262</v>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>2096</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>262</v>
-      </c>
       <c r="D8" s="7" t="n">
+        <v>1219.2</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>31.44</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>209.6</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>1886.4</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>419.2</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>1676.8</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>1219.2</v>
       </c>
     </row>
   </sheetData>
@@ -1346,13 +1321,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1394,219 +1369,1071 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Prix moyen TTC du litre de bière retenu par le service</t>
+          <t>CA liquides TTC avant abattements, exercice des annexes finales</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>16.38</v>
+        <v>165065.33</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>EUR/L</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>annexes finales : CA bière reconstitué / volume valorisé</t>
+          <t>bloc de synthese des annexes finales</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Abattements de fin de méthode appliqués au CA liquides</t>
+          <t>Chacun des trois forfaits de 5 % de fin de methode</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15</v>
+        <v>8253.27</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>5 % remise + 5 % pertes + 5 % conso personnel</t>
+          <t>5 % de 165 065,33 EUR TTC (remise, pertes, conso personnel)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Coefficient liquides -&gt; solides appliqué par le service</t>
+          <t>Total du second abattement (15 %) sur cet exercice</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>3.1</v>
+        <v>24759.81</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>CA solides = CA liquides après abattements x 3,10</t>
+          <t>8 253,27 EUR x 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>CA total reconstitué TTC entraîné par 1 litre de fût</t>
+          <t>Le meme forfait de 5 % chiffre par le service p. 72, 73 et 89</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>57.09</v>
+        <v>35133.26</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>EUR/L</t>
-        </is>
-      </c>
-      <c r="D8" s="4">
-        <f> prix du litre x (1 - 15 %) x (1 + 3,10)</f>
-        <v/>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>meme taux, mesure apres amplification cuisine et sur le premier exercice : 8 917,07 EUR de liquides (proposition p. 52) x 3,94 (1 + coefficient de revente 2,94). Ce n'est pas un autre forfait.</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Valeur du 1er abattement (15 % du fût), 3 exercices</t>
+          <t>Coefficient liquides -&gt; solides applique par le service</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>17948</v>
+        <v>3.1</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>314,4 L x 57,09 EUR/L</t>
+          <t>CA solides = CA liquides apres abattements x 3,10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Valeur du 2e abattement (15 % en fin de méthode) sur la seule bière</t>
+          <t>Taux reel retire par le service sur le fut</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>17948</v>
+        <v>27.75</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>267,2 L x 67,16 EUR/L</t>
+          <t>1 - 0,85 x 0,85 = 27,75 %, et non 30 %. Les annexes appliquent deja cette composition (63 200 cl - 9 480 cl = 53 720 cl, puis les forfaits sur le CA) : la correction ne modifie aucun montant.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Taux réel retiré par le service sur le fût</t>
+          <t>1er abattement du service, en litres de fut</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>27.75</v>
+        <v>314.4</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>et non 30 % : 1 - 0,85 x 0,85</t>
+          <t>15 % des 2 096 L achetes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Écart entre le taux revendiqué (30 %) et le taux réel</t>
+          <t>2e abattement du service, en equivalent-litres de fut</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>2.25</v>
+        <v>267.2</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>points de fût</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>soit 47,2 L sur 3 exercices</t>
+          <t>15 % du volume net, dont 89,1 L seulement au titre des pertes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Écart en CA total reconstitué TTC</t>
+          <t>Freinte retenue par la defense</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2692</v>
+        <v>121.9</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>aux paramètres du service (prix du litre et coefficient 3,10)</t>
-        </is>
+          <t>10 % de la biere reellement sortie du fut (1 219,2 L lus en caisse)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bière pression : freinte technique du fût et assiette des abattements</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SARL LA DEMI LUNE. Sources : factures FCBS, caisse (annexes C), annexes finales de la proposition de rectifications. Script : scripts/reponse1-biere-freinte.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Mois</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Bière servie au verre (L)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Jours avec vente de bière</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Litres par jour avec vente de bière</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Freinte retenue par la défense (10 % de la contenance servie)</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>soit 6,2 % du fût acheté, donc moins que les 15 % du service</t>
-        </is>
+        <v>3.4</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Volume résiduel jeté avec les fûts (262 x 120 ml)</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>31.44</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>manuel Heineken Blade : 1,5 % (120 ml) par fût</t>
+        <v>6</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bière pression : freinte technique du fût et assiette des abattements</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SARL LA DEMI LUNE. Sources : factures FCBS, caisse (annexes C), annexes finales de la proposition de rectifications. Script : scripts/reponse1-biere-freinte.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Fût percé le</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Périmé le</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Solde perdu (L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2023-02-23</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>2 fûts</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="76" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bière pression : freinte technique du fût et assiette des abattements</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SARL LA DEMI LUNE. Sources : factures FCBS, caisse (annexes C), annexes finales de la proposition de rectifications. Script : scripts/reponse1-biere-freinte.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Litres</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Source et portée exacte</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Volume résiduel admis dans un fût vide, jeté avec le fût</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>majorant documenté</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>262 fûts x 120 ml. Manuel Heineken Blade, ch. 6.3 « Dérangement, causes possibles et remèdes », p. 28 : « le volume résiduel acceptable s'élève à 1,5 % (120 ml) ». C'est un SEUIL DE TOLÉRANCE, donc un maximum admis, et non une perte moyenne mesurée sur nos fûts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Fûts non écoulés dans la durée de vie utile de 30 jours</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>simulé</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2 fûts, datés sur le calendrier des annexes C (hivers de fermeture) ; hypothèse la plus favorable au service (tout le fût acheté passe par le bec). Dans l'hypothèse inverse (seul le volume lu en caisse sort du fût) : 3 fûts et 13,1 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Total des deux seuls postes chiffrés par le constructeur</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>documenté</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>soit 1,57 % du fût acheté. Ce total ne comprend NI la mousse retirée au service, NI le moussage d'un fût mal pré-refroidi, NI la bière perdue au montage et au retrait des fûts, que le manuel décrit sans les chiffrer : ce n'est donc pas un taux de freinte et il ne peut pas être comparé au taux du service</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Freinte retenue par la défense (10 % de la bière réellement sortie du fût, 1 219,2 L lus en caisse)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>estimé</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>sources professionnelles convergentes, borne basse. Assiette corrigée : le mémoire du 10/07/2026 appliquait ce taux à la contenance des verres (1 292,9 L), qui comprend 73,7 L de limonade, de grenadine et de Picon jamais sortis du fût. 129 L -&gt; 121,9 L, soit 5,82 % du fût acheté</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Pour mémoire : le même taux de 10 % appliqué au fût acheté</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>209.6</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>non retenu</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>assiette que nous ne retenons pas, bien que ce soit celle des sources ; elle donnerait 209,6 L au lieu de 121,9 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Pour mémoire : borne haute des sources (20 % du fût)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>non retenu</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Modern Restaurant Management et OA Formation ; nous ne la demandons pas</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Premier abattement accordé par le service (15 % du fût)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>314.4</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>annexes finales : « consommation personnel et pertes »</t>
         </is>
       </c>
     </row>

--- a/public/documents/pieces-reponse-1/R1-biere-freinte.xlsx
+++ b/public/documents/pieces-reponse-1/R1-biere-freinte.xlsx
@@ -681,31 +681,31 @@
         <v>25</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>129</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>29.7</v>
+        <v>27.1</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>130</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>29.9</v>
+        <v>27.3</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>123.5</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>28.4</v>
+        <v>25.9</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>382.5</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>88</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="9">
@@ -718,31 +718,31 @@
         <v>50</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>37</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>66.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>30.6</v>
+        <v>27.9</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>59</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>27.1</v>
+        <v>24.8</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>162.5</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>74.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="10">
@@ -794,25 +794,25 @@
         <v>1497</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>431.7</v>
+        <v>427.6</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>1311.5</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>391.1</v>
+        <v>385.8</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>1323.5</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>396.4</v>
+        <v>391.6</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>4132</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>1219.2</v>
+        <v>1205</v>
       </c>
     </row>
   </sheetData>
@@ -902,7 +902,7 @@
         <v>792</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>431.7</v>
+        <v>427.6</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>43.2</v>
+        <v>42.8</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>11.88</v>
@@ -929,7 +929,7 @@
         <v>632</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>391.1</v>
+        <v>385.8</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>39.1</v>
+        <v>38.6</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>9.48</v>
@@ -956,7 +956,7 @@
         <v>672</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>396.4</v>
+        <v>391.6</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>39.6</v>
+        <v>39.2</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>10.08</v>
@@ -983,7 +983,7 @@
         <v>2096</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1219.2</v>
+        <v>1205</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>121.9</v>
+        <v>120.5</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>31.44</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>121.9</v>
+        <v>120.5</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>10 % de la biere reellement sortie du fut (1 219,2 L lus en caisse)</t>
+          <t>10 % de la biere reellement sortie du fut (1 205,0 L lus en caisse)</t>
         </is>
       </c>
     </row>
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="6">
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>46.2</v>
+        <v>45.7</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="7">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>76.5</v>
+        <v>75.8</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>79.5</v>
+        <v>78.8</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="9">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="10">
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>33.6</v>
+        <v>33.3</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="11">
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="12">
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="13">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="16">
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="17">
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="18">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>34.5</v>
+        <v>34.1</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="19">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>55.3</v>
+        <v>54.7</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="20">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>60.7</v>
+        <v>59.9</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="21">
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>53.8</v>
+        <v>53.1</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="22">
@@ -1881,13 +1881,13 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>68.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="23">
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="24">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="26">
@@ -1951,7 +1951,7 @@
         <v>4</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="27">
@@ -1961,13 +1961,13 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>20.7</v>
+        <v>20.2</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="28">
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="29">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>32.2</v>
+        <v>31.6</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="30">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>50.4</v>
+        <v>49.7</v>
       </c>
       <c r="C30" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="31">
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="32">
@@ -2041,13 +2041,13 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>73.3</v>
+        <v>72.7</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="33">
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="C33" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="34">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>39.4</v>
+        <v>39</v>
       </c>
       <c r="C34" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="35">
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="C35" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="36">
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="C36" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="37">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="C37" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="38">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>29.5</v>
+        <v>29.1</v>
       </c>
       <c r="C38" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>
@@ -2199,7 +2199,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
+          <t>2023-01-08</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.37</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="6">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="7">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2 fûts, datés sur le calendrier des annexes C (hivers de fermeture) ; hypothèse la plus favorable au service (tout le fût acheté passe par le bec). Dans l'hypothèse inverse (seul le volume lu en caisse sort du fût) : 3 fûts et 13,1 L</t>
+          <t>2 fûts, datés sur le calendrier des annexes C (hivers de fermeture) ; hypothèse la plus favorable au service (tout le fût acheté passe par le bec). Dans l'hypothèse inverse (seul le volume lu en caisse sort du fût) : 2 fûts et 3,3 L</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>32.8</v>
+        <v>39.8</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -2353,18 +2353,18 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>soit 1,57 % du fût acheté. Ce total ne comprend NI la mousse retirée au service, NI le moussage d'un fût mal pré-refroidi, NI la bière perdue au montage et au retrait des fûts, que le manuel décrit sans les chiffrer : ce n'est donc pas un taux de freinte et il ne peut pas être comparé au taux du service</t>
+          <t>soit 1,90 % du fût acheté. Ce total ne comprend NI la mousse retirée au service, NI le moussage d'un fût mal pré-refroidi, NI la bière perdue au montage et au retrait des fûts, que le manuel décrit sans les chiffrer : ce n'est donc pas un taux de freinte et il ne peut pas être comparé au taux du service</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Freinte retenue par la défense (10 % de la bière réellement sortie du fût, 1 219,2 L lus en caisse)</t>
+          <t>Freinte retenue par la défense (10 % de la bière réellement sortie du fût, 1 205,0 L lus en caisse)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>121.9</v>
+        <v>120.5</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>sources professionnelles convergentes, borne basse. Assiette corrigée : le mémoire du 10/07/2026 appliquait ce taux à la contenance des verres (1 292,9 L), qui comprend 73,7 L de limonade, de grenadine et de Picon jamais sortis du fût. 129 L -&gt; 121,9 L, soit 5,82 % du fût acheté</t>
+          <t>sources professionnelles convergentes, borne basse. Assiette corrigée : le mémoire du 10/07/2026 appliquait ce taux à la contenance des verres (1 292,9 L), qui comprend 87,9 L de limonade, de grenadine et de Picon jamais sortis du fût. 129 L -&gt; 120,5 L, soit 5,75 % du fût acheté</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>assiette que nous ne retenons pas, bien que ce soit celle des sources ; elle donnerait 209,6 L au lieu de 121,9 L</t>
+          <t>assiette que nous ne retenons pas, bien que ce soit celle des sources ; elle donnerait 209,6 L au lieu de 120,5 L</t>
         </is>
       </c>
     </row>
